--- a/results/final_N33_v5/validation/LOOCV.xlsx
+++ b/results/final_N33_v5/validation/LOOCV.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RBF</t>
+          <t>IDW</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.0771</v>
+        <v>1.1079</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8898</v>
+        <v>0.9343</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0441</v>
+        <v>-0.1134</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1839</v>
+        <v>-0.2525</v>
       </c>
     </row>
     <row r="3">
@@ -495,20 +495,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RBF</t>
+          <t>IDW</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.0484</v>
+        <v>1.0837</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8646</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0482</v>
+        <v>-0.1165</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1784</v>
+        <v>-0.2591</v>
       </c>
     </row>
     <row r="4">
@@ -524,20 +524,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RBF</t>
+          <t>IDW</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.961</v>
+        <v>1.0006</v>
       </c>
       <c r="E4" t="n">
-        <v>0.792</v>
+        <v>0.8266</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0578</v>
+        <v>-0.1152</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1352</v>
+        <v>-0.2308</v>
       </c>
     </row>
     <row r="5">
@@ -553,20 +553,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RBF</t>
+          <t>IDW</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.0196</v>
+        <v>1.0545</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8912</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0571</v>
+        <v>-0.118</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1429</v>
+        <v>-0.2225</v>
       </c>
     </row>
     <row r="6">
@@ -582,20 +582,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RBF</t>
+          <t>IDW</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5.0469</v>
+        <v>4.9056</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7344</v>
+        <v>3.8996</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2296</v>
+        <v>-0.49</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4344</v>
+        <v>-0.3551</v>
       </c>
     </row>
     <row r="7">
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9537</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6924</v>
+        <v>0.7141</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0302</v>
+        <v>0.0721</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3458</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="13">
@@ -789,16 +789,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.834</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6363</v>
+        <v>0.642</v>
       </c>
       <c r="F13" t="n">
-        <v>0.012</v>
+        <v>0.058</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4078</v>
+        <v>0.3752</v>
       </c>
     </row>
     <row r="14">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.792</v>
+        <v>0.8042</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6207</v>
+        <v>0.6038</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0138</v>
+        <v>0.0378</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2329</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="15">
@@ -847,16 +847,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9537</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6924</v>
+        <v>0.7141</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0302</v>
+        <v>0.0721</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3458</v>
+        <v>0.309</v>
       </c>
     </row>
     <row r="16">
@@ -876,16 +876,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.6426</v>
+        <v>1.6927</v>
       </c>
       <c r="E16" t="n">
-        <v>1.344</v>
+        <v>1.3867</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1044</v>
+        <v>0.186</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5364</v>
+        <v>0.5077</v>
       </c>
     </row>
   </sheetData>
